--- a/data/trans_bre/P15B_3_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P15B_3_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-25,87</t>
+          <t>-24,7</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-81,37%</t>
+          <t>-81,25%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-66,93; -22,59</t>
+          <t>-68,42; -26,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-31,81; -6,6</t>
+          <t>-34,18; -6,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,67; 5,04</t>
+          <t>-18,74; 4,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-45,91; -11,14</t>
+          <t>-45,58; -9,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -6,36</t>
+          <t>-100,0; -8,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 290,36</t>
+          <t>-100,0; 158,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-94,38; -45,51</t>
+          <t>-95,03; -37,38</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-15,46</t>
+          <t>-15,5</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-67,74%</t>
+          <t>-67,82%</t>
         </is>
       </c>
     </row>
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-45,86; -8,16</t>
+          <t>-44,41; -9,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,27; -6,91</t>
+          <t>-27,94; -7,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-32,88; -11,56</t>
+          <t>-31,7; -10,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,69; -0,65</t>
+          <t>-28,63; -2,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -13,76</t>
+          <t>-100,0; -15,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-95,01; -29,26</t>
+          <t>-96,4; -28,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-92,29; 10,17</t>
+          <t>-93,36; 2,77</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-19,96</t>
+          <t>-17,9</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-84,52%</t>
+          <t>-84,16%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-48,46; 8,96</t>
+          <t>-44,94; 10,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-28,06; -1,07</t>
+          <t>-29,42; -0,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,39; 17,98</t>
+          <t>-19,04; 19,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-39,32; -6,54</t>
+          <t>-35,01; -4,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-83,83; 38,52</t>
+          <t>-79,24; 41,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-91,31; 12,42</t>
+          <t>-89,05; 10,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-82,11; 272,05</t>
+          <t>-74,18; 303,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; -29,66</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-6,66</t>
+          <t>-6,16</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-38,36%</t>
+          <t>-37,14%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,59; 7,05</t>
+          <t>-18,92; 8,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-24,83; -6,19</t>
+          <t>-25,74; -6,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 8,88</t>
+          <t>-12,71; 10,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 4,46</t>
+          <t>-18,29; 4,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -21,55</t>
+          <t>-100,0; -33,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-75,09; 194,78</t>
+          <t>-75,41; 196,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-77,88; 64,64</t>
+          <t>-75,65; 71,77</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-15,96</t>
+          <t>-15,38</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-68,37%</t>
+          <t>-68,3%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-32,11; -11,88</t>
+          <t>-32,69; -11,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-22,03; -10,97</t>
+          <t>-22,25; -11,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,04; -1,39</t>
+          <t>-13,35; -1,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,26; -8,81</t>
+          <t>-23,51; -9,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-85,23; -41,38</t>
+          <t>-85,18; -39,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-88,9; -56,79</t>
+          <t>-88,49; -56,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-74,96; -9,8</t>
+          <t>-73,22; -6,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-82,96; -45,4</t>
+          <t>-82,23; -47,18</t>
         </is>
       </c>
     </row>
